--- a/data/trans_orig/IQ21A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ21A-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de veces que han estado hospitalizados a lo largo de estos últimos 12 meses</t>
+          <t>Menores según el número de veces que han estado hospitalizados a lo largo de estos últimos 12 meses (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,12 +721,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,69</t>
+          <t>1,0; 1,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,69</t>
+          <t>1,0; 1,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,43</t>
+          <t>1,0; 1,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,52</t>
+          <t>1,0; 4,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,39</t>
+          <t>1,0; 1,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,61</t>
+          <t>1,0; 2,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -861,14 +861,14 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1,0; 1,3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>1,0; 1,31</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 1,3</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -876,17 +876,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,35</t>
+          <t>1,0; 1,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,49</t>
+          <t>1,0; 1,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 31,19</t>
+          <t>1,0; 26,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,2</t>
+          <t>1,0; 1,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,3</t>
+          <t>1,04; 1,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 13,43</t>
+          <t>1,04; 13,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,63</t>
+          <t>1,0; 1,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,45</t>
+          <t>1,0; 1,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,39</t>
+          <t>1,14; 2,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,42</t>
+          <t>1,05; 1,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,1</t>
+          <t>1,13; 2,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,83</t>
+          <t>1,0; 1,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,43</t>
+          <t>1,0; 1,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,59</t>
+          <t>1,0; 1,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,13</t>
+          <t>1,0; 2,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,56</t>
+          <t>1,0; 1,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,26</t>
+          <t>1,0; 2,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,31</t>
+          <t>1,0; 1,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,43</t>
+          <t>1,0; 1,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,23</t>
+          <t>1,0; 1,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,26</t>
+          <t>1,05; 1,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,37</t>
+          <t>1,07; 1,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,76</t>
+          <t>1,06; 1,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,51</t>
+          <t>1,08; 1,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,71</t>
+          <t>1,09; 11,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,41</t>
+          <t>1,05; 1,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,23</t>
+          <t>1,16; 5,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">

--- a/data/trans_orig/IQ21A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ21A-Habitat-trans_orig.xlsx
@@ -741,12 +741,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,41</t>
+          <t>1,0; 1,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,16</t>
+          <t>1,0; 3,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,35</t>
+          <t>1,0; 1,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,58</t>
+          <t>1,0; 2,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,37 +856,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1,0; 1,36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1,0; 1,31</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1,0; 1,33</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>1,0; 1,3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 1,3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 1,31</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 1,38</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,58</t>
+          <t>1,0; 1,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 26,44</t>
+          <t>1,0; 25,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,28</t>
+          <t>1,04; 1,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 13,47</t>
+          <t>1,04; 12,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,59</t>
+          <t>1,0; 1,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,53</t>
+          <t>1,0; 1,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,43</t>
+          <t>1,14; 2,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,49</t>
+          <t>1,05; 1,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,07</t>
+          <t>1,17; 2,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,86</t>
+          <t>1,0; 1,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,51</t>
+          <t>1,0; 1,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,61</t>
+          <t>1,0; 1,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,98</t>
+          <t>1,0; 2,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,57</t>
+          <t>1,0; 1,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,41</t>
+          <t>1,0; 2,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,27</t>
+          <t>1,0; 1,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,44</t>
+          <t>1,0; 1,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,2</t>
+          <t>1,0; 1,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,36</t>
+          <t>1,07; 1,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,62</t>
+          <t>1,06; 1,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,54</t>
+          <t>1,1; 1,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 11,27</t>
+          <t>1,12; 11,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,38</t>
+          <t>1,04; 1,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,35</t>
+          <t>1,09; 1,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,86</t>
+          <t>1,15; 6,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
